--- a/tests/e2e/content-import/fixtures/08_assessment_questions.xlsx
+++ b/tests/e2e/content-import/fixtures/08_assessment_questions.xlsx
@@ -28,10 +28,10 @@
     <t>e2e-asm-01</t>
   </si>
   <si>
-    <t>Q-000001</t>
-  </si>
-  <si>
-    <t>Q-000002</t>
+    <t>e2e-q-01</t>
+  </si>
+  <si>
+    <t>e2e-q-02</t>
   </si>
 </sst>
 </file>
